--- a/盲测.xlsx
+++ b/盲测.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\week 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\my-profile\week 3_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10464"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9192" windowHeight="2988" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="方案摘要" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,17 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+  <si>
+    <t>月份</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -42,35 +35,126 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Alex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ben</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cathy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>力量训练</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普拉提</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总金额</t>
+    <t>产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销售额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总销售额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销量大于1500的月份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$C$2</t>
+  </si>
+  <si>
+    <t>$C$3</t>
+  </si>
+  <si>
+    <t>$C$4</t>
+  </si>
+  <si>
+    <t>$C$5</t>
+  </si>
+  <si>
+    <t>$C$6</t>
+  </si>
+  <si>
+    <t>$D$2</t>
+  </si>
+  <si>
+    <t>$D$3</t>
+  </si>
+  <si>
+    <t>$D$4</t>
+  </si>
+  <si>
+    <t>$D$5</t>
+  </si>
+  <si>
+    <t>$D$6</t>
+  </si>
+  <si>
+    <t>基准情景</t>
+  </si>
+  <si>
+    <t>创建者 Administrator 日期 2026/9/18</t>
+  </si>
+  <si>
+    <t>乐观情景</t>
+  </si>
+  <si>
+    <t>创建者 Administrator 日期 2026/9/18
+修改者 Administrator 日期 2026/9/18</t>
+  </si>
+  <si>
+    <t>悲观情景</t>
+  </si>
+  <si>
+    <t>方案摘要</t>
+  </si>
+  <si>
+    <t>可变单元格:</t>
+  </si>
+  <si>
+    <t>当前值:</t>
+  </si>
+  <si>
+    <t>结果单元格:</t>
+  </si>
+  <si>
+    <t>注释: “当前值”这一列表示的是在</t>
+  </si>
+  <si>
+    <t>建立方案汇总时，可变单元格的值。</t>
+  </si>
+  <si>
+    <t>每组方案的可变单元格均以灰色底纹突出显示。</t>
+  </si>
+  <si>
+    <t>基准情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐观情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悲观情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000/1500/2500/1000/1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000/3000/3500/4000/2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500/750/400/800/500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -78,7 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,16 +178,95 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -111,18 +274,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -404,189 +647,554 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:G21"/>
+  <sheetFormatPr defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="7" width="9.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="2:7" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="105.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20</v>
+      </c>
+      <c r="E6" s="14">
+        <v>20</v>
+      </c>
+      <c r="F6" s="14">
+        <v>25</v>
+      </c>
+      <c r="G6" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20</v>
+      </c>
+      <c r="E7" s="14">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14">
+        <v>25</v>
+      </c>
+      <c r="G7" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14">
+        <v>20</v>
+      </c>
+      <c r="F8" s="14">
+        <v>25</v>
+      </c>
+      <c r="G8" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20</v>
+      </c>
+      <c r="E9" s="14">
+        <v>20</v>
+      </c>
+      <c r="F9" s="14">
+        <v>25</v>
+      </c>
+      <c r="G9" s="14">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20</v>
+      </c>
+      <c r="E10" s="14">
+        <v>20</v>
+      </c>
+      <c r="F10" s="14">
+        <v>25</v>
+      </c>
+      <c r="G10" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="14">
+        <v>1500</v>
+      </c>
+      <c r="G12" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2500</v>
+      </c>
+      <c r="E13" s="14">
+        <v>2500</v>
+      </c>
+      <c r="F13" s="14">
+        <v>2500</v>
+      </c>
+      <c r="G13" s="14">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1500</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="14.4" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46266</v>
+        <v>46143</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="F2">
-        <f>D2*E2</f>
-        <v>600</v>
+        <f>C2*D2</f>
+        <v>5000</v>
       </c>
       <c r="G2">
-        <f>SUMIFS(F:F,B:B,"Alex")</f>
-        <v>2000</v>
+        <f>SUMIFS(F:F,B:B,"滑轮")</f>
+        <v>29500</v>
       </c>
       <c r="H2">
-        <f>COUNTIFS(C:C,"普拉提")</f>
-        <v>3</v>
+        <f>COUNTIFS(B:B,"滑轮",D:D,"&gt;=1500")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46266</v>
+        <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F8" si="0">D3*E3</f>
-        <v>400</v>
+        <f t="shared" ref="F3:F6" si="0">C3*D3</f>
+        <v>7500</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46267</v>
+        <v>46204</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="G4">
-        <f>SUMIFS(F:F,B:B,"Ben",C:C,"普拉提")</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46267</v>
+        <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46268</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>362500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="D7">
-        <v>350</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46269</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>400</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>800</v>
+      <c r="C11" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <scenarios current="2" sqref="D3 D4">
+    <scenario name="基准情景" locked="1" count="10" user="Administrator" comment="创建者 Administrator 日期 2026/9/18">
+      <inputCells r="C2" val="20"/>
+      <inputCells r="C3" val="20"/>
+      <inputCells r="C4" val="20"/>
+      <inputCells r="C5" val="20"/>
+      <inputCells r="C6" val="20"/>
+      <inputCells r="D2" val="1000"/>
+      <inputCells r="D3" val="1500"/>
+      <inputCells r="D4" val="2500"/>
+      <inputCells r="D5" val="1000"/>
+      <inputCells r="D6" val="1000"/>
+    </scenario>
+    <scenario name="乐观情景" locked="1" count="10" user="Administrator" comment="创建者 Administrator 日期 2026/9/18_x000a_修改者 Administrator 日期 2026/9/18">
+      <inputCells r="C2" val="25"/>
+      <inputCells r="C3" val="25"/>
+      <inputCells r="C4" val="25"/>
+      <inputCells r="C5" val="25"/>
+      <inputCells r="C6" val="25"/>
+      <inputCells r="D2" val="1000"/>
+      <inputCells r="D3" val="1500"/>
+      <inputCells r="D4" val="2500"/>
+      <inputCells r="D5" val="1000"/>
+      <inputCells r="D6" val="1000"/>
+    </scenario>
+    <scenario name="悲观情景" locked="1" count="10" user="Administrator" comment="创建者 Administrator 日期 2026/9/18">
+      <inputCells r="C2" val="10"/>
+      <inputCells r="C3" val="8"/>
+      <inputCells r="C4" val="9"/>
+      <inputCells r="C5" val="11.5"/>
+      <inputCells r="C6" val="12"/>
+      <inputCells r="D2" val="1000"/>
+      <inputCells r="D3" val="1500"/>
+      <inputCells r="D4" val="2500"/>
+      <inputCells r="D5" val="1000"/>
+      <inputCells r="D6" val="1000"/>
+    </scenario>
+  </scenarios>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
